--- a/assessment_forms/028_legal_writing_skills_assessment--assessment_forms.xlsx
+++ b/assessment_forms/028_legal_writing_skills_assessment--assessment_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -980,12 +980,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>additional_file1</t>
+          <t>additional_file1_2</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Another additional file</t>
+          <t>Additional File1 2</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
@@ -1008,7 +1008,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Additional document 1</t>
+          <t>Uploaded Additional1</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
@@ -1026,12 +1026,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>uploaded_file</t>
+          <t>uploaded_file_2</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Another document</t>
+          <t>Uploaded File 2</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
@@ -1049,7 +1049,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>additional_file4</t>
+          <t>additional_file4_2</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1077,7 +1077,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Another file</t>
+          <t>Uploaded File3</t>
         </is>
       </c>
       <c r="D28" t="inlineStr"/>
